--- a/backend/elderlycare-common/src/main/resources/excel_model/ServiceItem.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/ServiceItem.xlsx
@@ -445,14 +445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,11 +475,6 @@
           <t>周期</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,11 +497,6 @@
           <t>period</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -528,11 +517,6 @@
           <t>月</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -553,11 +537,6 @@
           <t>月</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -576,11 +555,6 @@
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>月</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
         </is>
       </c>
     </row>
